--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-07-13 23:38 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-07-14 23:37 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>1900</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-07-18 23:38 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-07-19 23:42 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>1911</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-07-21 23:44 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-07-22 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>1913</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-07-22 23:46 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-07-23 23:44 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-07-23 23:44 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-07-24 23:48 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-07-24 23:48 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-07-25 23:46 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-07-27 23:49 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-07-28 23:44 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>1916</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-08-08 23:13 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-08-09 23:14 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
         <v>1938</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-08-17 23:03 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-08-18 23:04 UTC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
         <v>1956</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-08-22 23:02 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-08-23 23:02 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>1969</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-08-23 23:02 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-08-24 23:09 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-08-24 23:09 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-08-25 23:12 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-08-25 23:12 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-08-27 04:05 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-01 01:26 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-02 00:35 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>1979</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>

--- a/reports/竞品VOC周报.xlsx
+++ b/reports/竞品VOC周报.xlsx
@@ -622,7 +622,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-03 00:45 UTC</t>
+          <t>咖啡茶饮类目5个App · 负面=1-2星 · 评论样本有幸存者偏差（趋势与对比有效）· 生成于 2026-09-04 00:28 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         <v>1982</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
